--- a/app/data/insights.xlsx
+++ b/app/data/insights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ousmane/Desktop/2025 - Documentations/Python/Economics/genesis-research/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7554A7B8-E812-1145-9ED6-D8B470C8AAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F374EE-E583-FE4F-8DAE-6B6280D933BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="27200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="25540" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Insights" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="162">
   <si>
     <t>ID</t>
   </si>
@@ -46,12 +46,18 @@
     <t>Margins Under Pressure</t>
   </si>
   <si>
+    <t>September's ISM Manufacturing survey kept the sector in a soft patch, with the headline PMI rising slightly to 49.1 from 48.7 previously and just above the 49.0 expected — still signaling contraction.</t>
+  </si>
+  <si>
     <t>03-10-2025</t>
   </si>
   <si>
     <t>Sticky Prices, Cooling Demand</t>
   </si>
   <si>
+    <t>The September ISM Services survey showed a clear loss of momentum, with the headline PMI falling to 50.0 from 52.0 previously and slightly below the 51.7 expected — right at the edge of contraction.</t>
+  </si>
+  <si>
     <t>05-10-2025</t>
   </si>
   <si>
@@ -70,27 +76,42 @@
     <t>10‑Year Treasury vs DXY: Easing Path &amp; the Insurance Cut</t>
   </si>
   <si>
+    <t>The Fed's first 'insurance cut' marked a shift in tone, not direction, leaving the 10-year yield steady near 4% as the DXY rebounded from 96 to about 99.</t>
+  </si>
+  <si>
     <t>10-10-2025</t>
   </si>
   <si>
     <t>Inflation Psychology: Relief at 1-Year, Steady at 5-Year</t>
   </si>
   <si>
+    <t>Inflation expectations stabilized in October, with the 1-year measure easing to 4.6% from 4.7% previously and slightly above the 4.5% expected, signaling mild relief at the consumer level.</t>
+  </si>
+  <si>
     <t>Confidence Slips, Momentum Risks Ahead</t>
   </si>
   <si>
+    <t>October's Michigan survey came in at 55.0, unchanged from 55.1 previously and slightly above the 54.2 expected, showing confidence has plateaued.</t>
+  </si>
+  <si>
     <t>11-10-2025</t>
   </si>
   <si>
     <t>Gold and Geopolitics: From Relief to Resilience</t>
   </si>
   <si>
+    <t>Gold's post-FOMC rally peaked near $4,050 as Hamas accepted Trump's peace plan ending two years of war in Gaza, briefly releasing geopolitical risk—but the metal's resilience held when new tensions emerged.</t>
+  </si>
+  <si>
     <t>Equities</t>
   </si>
   <si>
     <t>Trump Shock: Tariff Risk Reprices, Sentiment Partially Rebounds</t>
   </si>
   <si>
+    <t>Donald Trump's threat of 'massive' tariffs on China triggered one of the sharpest equity sell-offs since April's Liberation Day shock, but weekend prediction-market trading showed a partial sentiment rebound.</t>
+  </si>
+  <si>
     <t>14-10-2025</t>
   </si>
   <si>
@@ -106,21 +127,33 @@
     <t>Manufacturing Regains Momentum, Inflation Pressures Persist</t>
   </si>
   <si>
+    <t>The NY Fed Empire State Manufacturing Index surged to 10.7 in October (from −8.7 and vs −1 expected), erasing September's dip and confirming that regional factory activity is regaining traction.</t>
+  </si>
+  <si>
     <t>Dow Jones Fades the 76.4% Fibonacci</t>
   </si>
   <si>
+    <t>The Dow's rebound failed at the 76.4% retracement near 46,675, confirming a shift from 'buy-the-dip' to 'sell-the-rip' and reinforcing the idea that markets have been choppy since the Trump announcement.</t>
+  </si>
+  <si>
     <t>16-10-2025</t>
   </si>
   <si>
     <t>Philly Fed: Headline Craters, Internals Hold Up</t>
   </si>
   <si>
+    <t>The Philadelphia Fed Manufacturing Index collapsed to −12.8 in October (from 23.2, cons 10), marking a 36-point swing into contraction, but the internals stayed firm.</t>
+  </si>
+  <si>
     <t>17-10-2025</t>
   </si>
   <si>
     <t>Bank Fragility Watch — Zions Sits on the 61.8%</t>
   </si>
   <si>
+    <t>Regional banks are again flashing stress as equities wobble. Zions Bancorporation has pulled back to the 61.8% retracement near 47, measured from the Liberation-Day low to the October high — a pivotal level for the regional-bank tape.</t>
+  </si>
+  <si>
     <t>21-10-2025</t>
   </si>
   <si>
@@ -136,18 +169,30 @@
     <t>Tactical Update — US30: Retesting the 76.4% Fade Amid Renewed Animal Spirits</t>
   </si>
   <si>
+    <t>US30 rebounded sharply to start the week, rising more than 1 % alongside a 2 % surge in gold, as risk appetite returned on optimism over U.S.–China trade talks and a potential end to the government shutdown.</t>
+  </si>
+  <si>
     <t>Gold Tactical Play 2 — Buying the Dip at the 61.8% Confluence</t>
   </si>
   <si>
+    <t>Gold’s rebound from the October 17 flush confirmed the market’s buy-the-dip instinct, with a perfect technical alignment at the 61.8 % retracement and 1-hour MA 100.</t>
+  </si>
+  <si>
     <t>Gold Holds 61.8% After Washout — Eyes on 78.6% for Second Entry</t>
   </si>
   <si>
+    <t>Gold defended the 61.8% retracement (~4110) after a near –5% wash-out—the worst single-day drop since the pandemic—keeping the uptrend intact but fragile.</t>
+  </si>
+  <si>
     <t>23-10-2025</t>
   </si>
   <si>
     <t>Kansas Fed: Regional Strength Amid Mixed Signals</t>
   </si>
   <si>
+    <t>The Kansas City Fed’s Manufacturing Production Index surged to 15 — the strongest since April 2022 — outpacing the Composite Index (6) and signaling renewed regional strength in output momentum.</t>
+  </si>
+  <si>
     <t>24-10-2025</t>
   </si>
   <si>
@@ -163,12 +208,18 @@
     <t>Dallas Fed: Weak Pulse, Strong Signal</t>
   </si>
   <si>
+    <t>Texas manufacturing steadied in October as production held firm while demand and sentiment stayed soft — a sign of stabilization, not acceleration.</t>
+  </si>
+  <si>
     <t>28-10-2025</t>
   </si>
   <si>
     <t>Richmond Fed: Pessimism Fades, Recovery Broadens</t>
   </si>
   <si>
+    <t>The Richmond Fed’s rebound to −4 from −17 marked the softest pessimism since March, signaling that factory sentiment is stabilizing as demand improves.</t>
+  </si>
+  <si>
     <t>01-11-2025</t>
   </si>
   <si>
@@ -184,12 +235,18 @@
     <t>FOMC: The Cut Was Dovish, The Read Was Hawkish</t>
   </si>
   <si>
+    <t>The Fed cut 25 bp to 3.75–4.00 %, but markets priced it hawkish: DXY firmed, the 10-year rebounded toward 4 %, and December cut odds slid to ~67 % from ~90 %.</t>
+  </si>
+  <si>
     <t>31-10-2025</t>
   </si>
   <si>
     <t>Gold Reclaims 4,000 as the 78.6% Pivot Holds</t>
   </si>
   <si>
+    <t>Gold defended the 78.6% retracement near 3,915 — aligned with the 4-hour MA200 — marking a second successful defense of structural support.</t>
+  </si>
+  <si>
     <t>02-11-2025</t>
   </si>
   <si>
@@ -211,21 +268,33 @@
     <t>Oil’s Drop Offsets Tariff Inflation — Reinforcing the Soft-Landing Path</t>
   </si>
   <si>
+    <t>Falling oil prices are offsetting tariff-driven inflation, preserving the disinflation narrative and reinforcing the Fed’s soft-landing path ahead of the next CPI print.</t>
+  </si>
+  <si>
     <t>Gold: Precision Execution, Same Structure, New Setup</t>
   </si>
   <si>
+    <t>Our initial gold position was perfectly executed — 400 pips in profit, partial profits taken, and the remaining position moved to break-even, keeping the setup risk-free.</t>
+  </si>
+  <si>
     <t>04-11-2025</t>
   </si>
   <si>
     <t>Dow Jones at the Channel Top — Soft-Landing or Overstretch?</t>
   </si>
   <si>
+    <t>The Dow has reached the upper bound of its ascending channel from the 2022 lows — a sign of strength but also a potential exhaustion point amid stretched AI valuations.</t>
+  </si>
+  <si>
     <t>Cross-Asset</t>
   </si>
   <si>
     <t>Seasonality and the Dollar: A Familiar Year-End Setup</t>
   </si>
   <si>
+    <t>Even as the Dow tests its 2022 up-channel and the dollar stalls near its July peak, cross-market seasonality argues that year-end support remains the base case.</t>
+  </si>
+  <si>
     <t>05-11-2025</t>
   </si>
   <si>
@@ -238,15 +307,27 @@
     <t>ISM Services: Inflation Floor, Not a Pivot</t>
   </si>
   <si>
+    <t>ISM Services beat across the board — 52.4 vs 50.8 cons and 50.0 prior — but prices surprised higher to 70.0, keeping the inflation floor in place.</t>
+  </si>
+  <si>
     <t>ISM Prices vs CPI — Goods Relief, Services Resistance</t>
   </si>
   <si>
+    <t>Manufacturing prices keep easing while services prices surge, leaving CPI on a slow-disinflation path rather than a clean break lower.</t>
+  </si>
+  <si>
     <t>Services Activity Echoes Earlier Yield Decline</t>
   </si>
   <si>
+    <t>Services activity is re-accelerating just as the earlier drop in long-term yields — advanced 18 months — said it would, keeping the U.S. in a 1–2% Goldilocks growth band even as hiring lags.</t>
+  </si>
+  <si>
     <t>Gold: Deeper Dip, Same Bullish Structure</t>
   </si>
   <si>
+    <t>Gold absorbed a deeper intraday flush than we first mapped — breaking 3,989.10 and tagging the 61.8% of the consolidation near 3,944 — but the structure held and dip-buying returned even after a stronger ADP.</t>
+  </si>
+  <si>
     <t>Dow: Tactical Short Zone Defined — Between 47,465 and 47,599</t>
   </si>
   <si>
@@ -259,21 +340,36 @@
     <t>Dollar at the Crossroads — Short Limit at 100.25 Confirms the Turn</t>
   </si>
   <si>
+    <t>The DXY rejected 100.25 — the 50% retracement of the 104.68–96.22 range — confirming that the dollar’s rebound has stalled at the same confluence that capped upside since midyear.</t>
+  </si>
+  <si>
     <t>07-11-2025</t>
   </si>
   <si>
     <t>Confidence Crack — Consumption Next, Conditions Ease</t>
   </si>
   <si>
+    <t>Michigan sentiment fell to 50.3 from 53.6 and below the 53.2 expected, signaling a confidence crack that precedes slower consumption and a near-term wobble in risk appetite.</t>
+  </si>
+  <si>
     <t>Inflation Expectations Split: Short-Term Up, Long-Term Down</t>
   </si>
   <si>
+    <t>Inflation expectations split in November: Michigan 1-year rose to 4.7 (from 4.6, vs 4.6), Michigan 5-year eased to 3.6 (from 3.9, vs 3.9), and NY Fed 1-year fell to 3.2 (from 3.4).</t>
+  </si>
+  <si>
     <t>US30: Playbook Respected — Short Zone Holds, Bounce at 4h-200</t>
   </si>
   <si>
+    <t>The Dow faded at 47,464, bounced off ~46,500 and the 4h-MA200, and now sits mid-range; we keep the short bias but will observe price action and prep the next move after sizable partial profits.</t>
+  </si>
+  <si>
     <t>Gold: Two Precision Entries, Core Long Riding to 4,050</t>
   </si>
   <si>
+    <t>After a 4h-MA200 break and a 78.6% tag, gold delivered two precise longs—3984.28 and the earlier 3966.87—with profits taken at 4020 and a risk-free core now riding toward 4050.</t>
+  </si>
+  <si>
     <t>10-11-2025</t>
   </si>
   <si>
@@ -307,9 +403,15 @@
     <t>Kansas Beats, ISM Sub-50 — Stabilization, Not Reacceleration</t>
   </si>
   <si>
+    <t>Kansas City manufacturing strengthened: Production 18 (from 15, vs 12) and Composite 8 (from 6, vs 4), outpacing a still-sub-50 ISM.</t>
+  </si>
+  <si>
     <t>Claims Split: Flow Cools, Stock Builds</t>
   </si>
   <si>
+    <t>Initial claims fell to 220k (from 229k, vs 262k) while continuing claims rose to 1.974M (from 1.946M, vs 1.970M), implying labor loosens at the margins.</t>
+  </si>
+  <si>
     <t>Labor Cools, Not Cracks — Mixed Print, Softer Edges</t>
   </si>
   <si>
@@ -322,6 +424,9 @@
     <t>Minutes Measured, Williams Dovish — December Is Live, Not Locked</t>
   </si>
   <si>
+    <t>Minutes stayed measured while Williams leaned dovish, keeping December live—not locked—and re-easing conditions.</t>
+  </si>
+  <si>
     <t>Inflation Expectations Ease — 5y5y Flags Growth Angst</t>
   </si>
   <si>
@@ -331,21 +436,33 @@
     <t>Confidence Still Low — Spending Cools Next, Growth Slows</t>
   </si>
   <si>
+    <t>Michigan sentiment rose to 51.0 (from 50.3); Current Conditions 51.1 (vs 52.3) fell, Expectations 51 (vs 49) improved—still a late-cycle mix pointing to cooler consumption and slower growth.</t>
+  </si>
+  <si>
     <t>22-11-2025</t>
   </si>
   <si>
     <t>Seasonality vs YTD — Gold Leads, Tech Wobbles</t>
   </si>
   <si>
+    <t>The S&amp;P 500 is pulling back in line with seasonality as gold leads and Bitcoin lags; with USD and bonds mixed into December FOMC, a year-end rebound window remains open but unconfirmed.</t>
+  </si>
+  <si>
     <t>24-11-2025</t>
   </si>
   <si>
     <t>Dallas Diverges — Headline Contracts, Output Jumps, Prices Cool</t>
   </si>
   <si>
+    <t>Dallas manufacturing fell to −10.4 (from −5, vs −1), while production jumped to 20.5 and prices paid cooled, highlighting a split between weak sentiment and firmer output.</t>
+  </si>
+  <si>
     <t>Gold Reclaims 4,100 — 4h MA200 Holds, Buy Dips</t>
   </si>
   <si>
+    <t>Gold holds the 4h-MA200 and trades ~4,122 after last week’s relief dip; the uptrend favors buying orderly pullbacks while 4,245.02 remains the key obstacle to confirm momentum toward prior highs.</t>
+  </si>
+  <si>
     <t>AI Mania — Bubble Pathways and a Breadth Warning</t>
   </si>
   <si>
@@ -355,862 +472,47 @@
     <t>December Cut Odds Surge — Gold Tailwind Reaffirmed</t>
   </si>
   <si>
-    <t>December cut odds rose to ~81% (from ~65% last week; ~20% pre-Williams), easing conditions and reinforcing our gold-on-dips map from 4,053.43 while equity relief stays tentative.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Michigan sentiment rose to 51.0 (from 50.3)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>; Current Conditions 51.1 (vs 52.3) fell, Expectations 51 (vs 49) improved—still a late-cycle mix pointing to cooler consumption and slower growth.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The S&amp;P 500 is pulling back in line with seasonality as gold leads and Bitcoin lags</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>; with USD and bonds mixed into December FOMC, a year-end rebound window remains open but unconfirmed.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dallas manufacturing fell to −10.4 (from −5, vs −1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, while production jumped to 20.5 and prices paid cooled, highlighting a split between weak sentiment and firmer output.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gold holds the 4h-MA200 and trades ~4,122 after last week’s relief dip</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>; the uptrend favors buying orderly pullbacks while 4,245.02 remains the key obstacle to confirm momentum toward prior highs.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Minutes stayed measured while Williams leaned dovish</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, keeping December live—not locked—and re-easing conditions.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Initial claims fell to 220k (from 229k, vs 262k) while continuing claims rose to 1.974M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (from 1.946M, vs 1.970M),</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> implying labor loosens at the margins.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>September's ISM Manufacturing survey kept the sector in a soft patch, with the headline PMI rising slightly to 49.1 from 48.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> previously and just above the 49.0 expected — still signaling contraction.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The September ISM Services survey showed a clear loss of momentum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, with the headline PMI falling to 50.0 from 52.0 previously and slightly below the 51.7 expected — right at the edge of contraction.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Fed's first 'insurance cut' marked a shift in tone, not direction, leaving the 10-year yield steady near 4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> as the DXY rebounded from 96 to about 99.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Inflation expectations stabilized in October,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> with the 1-year measure easing to 4.6% from 4.7% previously and slightly above the 4.5% expected, signaling mild relief at the consumer level.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>October's Michigan survey came in at 55.0, unchanged</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> from 55.1 previously and slightly above the 54.2 expected, showing confidence has plateaued.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gold's post-FOMC rally peaked near $4,050 as Hamas accepted Trump's peace plan ending two years of war in Gaza</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, briefly releasing geopolitical risk—but the metal's resilience held when new tensions emerged.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Donald Trump's threat of 'massive' tariffs on China triggered one of the sharpest equity sell-offs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> since April's Liberation Day shock, but weekend prediction-market trading showed a partial sentiment rebound.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The NY Fed Empire State Manufacturing Index surged to 10.7 in October (from −8.7 and vs −1 expected)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, erasing September's dip and confirming that regional factory activity is regaining traction.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Dow's rebound failed at the 76.4% retracement near 46,675, confirming a shift from 'buy-the-dip' to 'sell-the-rip'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and reinforcing the idea that markets have been choppy since the Trump announcement.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Philadelphia Fed Manufacturing Index collapsed to −12.8 in October (from 23.2, cons 10)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, marking a 36-point swing into contraction, but the internals stayed firm.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Regional banks are again flashing stress as equities wobble. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Zions Bancorporation has pulled back to the 61.8% retracement near 47, measured from the Liberation-Day low to the October high — a pivotal level for the regional-bank tape.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>US30 rebounded sharply to start the week</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, rising more than 1 % alongside a 2 % surge in gold, as risk appetite returned on optimism over U.S.–China trade talks and a potential end to the government shutdown.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gold’s rebound from the October 17 flush confirmed the market’s buy-the-dip instinct</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, with a perfect technical alignment at the 61.8 % retracement and 1-hour MA 100.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Gold defended the 61.8% retracement (~4110) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>after a near –5% wash-out—the worst single-day drop since the pandemic—keeping the uptrend intact but fragile.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Kansas City Fed’s Manufacturing Production Index surged to 15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> — the strongest since April 2022 — outpacing the Composite Index (6) and signaling renewed regional strength in output momentum.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Texas manufacturing steadied </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>in October as production held firm while demand and sentiment stayed soft — a sign of stabilization, not acceleration.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Richmond Fed’s rebound to −4 from −17 marked the softest pessimism since March</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, signaling that factory sentiment is stabilizing as demand improves.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Fed cut 25 bp to 3.75–4.00 %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> but markets priced it hawkish</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>: DXY firmed, the 10-year rebounded toward 4 %, and December cut odds slid to ~67 % from ~90 %.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gold defended the 78.6% retracement near 3,915</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> — aligned with the 4-hour MA200 — marking a second successful defense of structural support.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Falling oil prices are offsetting tariff-driven inflation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, preserving the disinflation narrative and reinforcing the Fed’s soft-landing path ahead of the next CPI print.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Our initial gold position was perfectly executed — 400 pips in profit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, partial profits taken, and the remaining position moved to break-even, keeping the setup risk-free.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Dow has reached the upper bound of its ascending channel from the 2022 lows</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> — a sign of strength but also a potential exhaustion point amid stretched AI valuations.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Even as the Dow tests its 2022 up-channel and the dollar stalls near its July peak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, cross-market seasonality argues that year-end support remains the base case.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ISM Services beat across the board — 52.4 vs 50.8 cons and 50.0 prior </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>— but prices surprised higher to 70.0, keeping the inflation floor in place.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Manufacturing prices keep easing while services prices surge,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> leaving CPI on a slow-disinflation path rather than a clean break lower.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Services activity is re-accelerating just as the earlier drop in long-term yields </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>— advanced 18 months — said it would, keeping the U.S. in a 1–2% Goldilocks growth band even as hiring lags.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gold absorbed a deeper intraday flush than we first mapped</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> — breaking 3,989.10 and tagging the 61.8% of the consolidation near 3,944 — but the structure held and dip-buying returned even after a stronger ADP.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">The DXY rejected 100.25 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>— the 50% retracement of the 104.68–96.22 range — confirming that the dollar’s rebound has stalled at the same confluence that capped upside since midyear.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Michigan sentiment fell to 50.3 from 53.6 and below the 53.2 expected</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, signaling a confidence crack that precedes slower consumption and a near-term wobble in risk appetite.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Inflation expectations split in November: Michigan 1-year rose to 4.7 (from 4.6, vs 4.6)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, Michigan 5-year eased to 3.6 (from 3.9, vs 3.9), and NY Fed 1-year fell to 3.2 (from 3.4).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Dow faded at 47,464, bounced off ~46,500 and the 4h-MA200, and now sits mid-range; we keep the short bias but will observe price action and prep the next move after sizable partial pr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ofits.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>After a 4h-MA200 break and a 78.6% tag, gold delivered two precise longs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>—3984.28 and the earlier 3966.87—with profits taken at 4020 and a risk-free core now riding toward 4050.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Kansas City manufacturing strengthened</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>: Production 18 (from 15, vs 12) and Composite 8 (from 6, vs 4), outpacing a still-sub-50 ISM.</t>
-    </r>
+    <t>December cut odds rose to ~75% (from above than 50% last week; ~20% pre-Williams), easing conditions and reinforcing our gold-on-dips map from 4,053.43 while equity relief stays tentative.</t>
+  </si>
+  <si>
+    <t>25-11-2025</t>
+  </si>
+  <si>
+    <t>Retail Sales Miss Under the Hood — Consumption Cools</t>
+  </si>
+  <si>
+    <t>Retail sales slowed to 0.2% m/m in Sep (from 0.6, vs 0.4) and the control group fell −0.1% (from 0.6, vs 0.3), signaling softer consumption ahead even as YoY held 4.3% (vs 3.9).</t>
+  </si>
+  <si>
+    <t>Pipeline Cool: Core PPI Eases, Survey Costs Lead Lower</t>
+  </si>
+  <si>
+    <t>Core PPI slowed to 2.6% YoY (from 2.9, vs 2.7) while headline PPI held at 2.7% (vs 2.7), keeping pipeline inflation stable-to-cooling.</t>
+  </si>
+  <si>
+    <t>Richmond Plunge Rejoins Dallas — ISM Risk Skews Lower</t>
+  </si>
+  <si>
+    <t>Richmond manufacturing fell to −15 (from −4, vs −2) with shipments −14 (from 4, vs 6), reinforcing Dallas weakness and tilting near-term ISM risk to the downside.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Mixed</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>Positive</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1223,13 +525,22 @@
       <sz val="10"/>
       <color rgb="FFE5E7EB"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1247,12 +558,12 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFC00000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1283,6 +594,24 @@
         <bgColor rgb="FF4B5563"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1311,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1332,9 +661,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1637,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1647,7 +980,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1664,7 +997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1678,928 +1011,1159 @@
         <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>48</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>111</v>
+      <c r="D56" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D61" s="9" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/app/data/insights.xlsx
+++ b/app/data/insights.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>10s–2s Back Above Zero — Risk Shifts to the Cut Phase</t>
+          <t>YIELD CURVE ANALYSIS 1/4 — Re-Steepening &amp; Jobs</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -2124,26 +2124,201 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>26-11-2025</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>YIELD CURVE ANALYSIS 2/4 — Claims vs Unemployment</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Unemployment has risen ~1pp from lows while initial claims stay subdued—pointing to hiring freezes over layoffs, but a break would come if claims trend &gt;240–250k or continuing &gt;2.0M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>26-11-2025</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>YIELD CURVE ANALYSIS 3/4 — Policy Reaction Function</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>The inflation–unemployment spread remains elevated, limiting the pace of easing even as growth risks rise—cuts likely, but measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>26-11-2025</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>YIELD CURVE ANALYSIS 4/4 — Prices, Oil, and the Last Mile</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>ISM Prices sit in the high-50s while oil trends lower—macro mix that cools headline pressure and supports a glide-path disinflation case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>26-11-2025</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Currencies</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Yield Spread Compresses — USD Headwind Builds</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>US–G4 ex-US (EA/JP/UK/CAD) 10Y spread compresses toward ~1pp while DXY stalls below its 200-day—conditions that typically tilt the dollar softer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>26-11-2025</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>ISM vs Regions — Activity Stabilizes, Prices Still Hotter Locally</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing looks flat-to-slightly higher, while our Regional Fed Prices-Paid tracker remains elevated near a +1σ high versus ISM Prices at 60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>01-12-2025</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>ISM 48.2 — Orders Weaken, Employment Slips, Prices Stay Firm</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>ISM fell to 48.2 in November (from 48.7, vs 49.0), with new orders 47.4 and prices 58.5 while employment slid to 44.0—demand cools as cost pressure persists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>01-12-2025</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Silver Surge, Ratio Collapse — Gold Tailwind Strengthens</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Gold/silver ratio has slid to ~70 (from ~100 in April) as silver makes fresh highs—historically, such compressions precede further gold upside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>01-12-2025</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Gold Breaks 4,245 — Next Resistance ~4,381</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Gold hit 4,245 (our level) and breaks higher; next resistance ~4,381 with support 4,120/4,053 as policy easing and a softer USD extend the bid.</t>
         </is>
       </c>
     </row>

--- a/app/data/insights.xlsx
+++ b/app/data/insights.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2322,6 +2322,156 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Equities</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Santa Drift, NVDA Lags — Rotation Builds</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Year-end rebound resumes: SPX/NASDAQ/Mag7 back above MA50 while NVDA lags—rotation favors GOOG and broad-market lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>ADP −32k — Hiring Momentum Breaks, NFP Bias Lower</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>ADP fell −32k in November (vs +42k prior, +10k cons), signaling a break in private hiring and tilting NFP risks lower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Import Prices Turn Up — Softer Dollar Starts to Bite</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Import prices likely rose 0.6% m/m (from 0.0, vs 0.6 cons), a lagged lift from a softer dollar that slows the last mile without stopping it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>ISM Services — 10Y Leads Activity; Prices Cool, Jobs Firm</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>10-year yield change (advanced 12m) points to steady services activity; prices fell to 65.4 while employment improved—easier conditions and a softer dollar favor a soft-landing mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Gold Holds Break, Silver Prints Records — Cuts Near, Dips Bought</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Gold cleared 4,245 and held a 38.2% retrace of the 3,998.09→4,264.29 impulse as silver hits fresh records—soft labor and ~90% cut odds extend the bid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>04-12-2025</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Claims Plunge — Flow 191k, Stock Eases</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Initial claims fell to 191k (from 218k, vs 220k) and continuing claims dipped to 1.939M (from 1.943M, vs 1.960M)—flow and stock both eased, tempering slowdown fears ahead of NFP.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/data/insights.xlsx
+++ b/app/data/insights.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2472,6 +2472,106 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>05-12-2025</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Core 2.8%, Headline 2.8 — Last-Mile Eases, Not Re-Accelerates</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Core PCE eased to 2.8% annual (from 2.9; 0.2% m/m) while headline held 2.8% (0.3% m/m)—disinflation inches forward and keeps measured easing in play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>05-12-2025</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Sentiment 53.3; Expectations 55 — Cushion Firms, Not Roars</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>UMich sentiment rose to 53.3 and expectations to 55 while current conditions dipped to 50.7—forward tone improves even as today’s cushion stays thin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>05-12-2025</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Currencies</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Yen Ignores Narrowing Spread — Regime Shift Risk</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Since April, the inverted US–Japan 10Y spread narrowed ~150bp while USD/JPY rose to ~155—We think this decoupling is temporary and expect yen appreciation into 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>05-12-2025</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Labor Demand Cools, Price Leads Roll — 2026 Growth Risk</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Openings per unemployed are falling and price leads have rolled over, yet PCE lingers near 3%—growth likely slows first while disinflation grinds into 2026.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
